--- a/source-excel/L1L2.xlsx
+++ b/source-excel/L1L2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\รายงานการจัดระดับ\ข้อมูลทำ AI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\รายงานการจัดระดับ\ข้อมูลทำ AI\newstarrating\source-excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{196F125D-11CD-4A2D-9B12-F2E17C81A11B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8095D496-061C-4F84-B68F-C9387DA3F401}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8130" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,6 +23,7 @@
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">L1L2!$A$4:$Q$880</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Score!$A$1:$H$288</definedName>
     <definedName name="_xlnm.Database">[1]ข้อมูล!$B$11:$H$11</definedName>
     <definedName name="Datalist">OFFSET('[2]Data-CPAC'!$A$1,0,0,COUNTA('[2]Data-CPAC'!$A:$A),COUNTA('[2]Data-CPAC'!$1:$1))</definedName>
     <definedName name="DAYS">[1]ข้อมูล!$J$12:$L$198</definedName>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16695" uniqueCount="3211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16696" uniqueCount="3212">
   <si>
     <t>รหัสพนักงาน</t>
   </si>
@@ -9806,6 +9807,9 @@
   </si>
   <si>
     <t>หจก.เซ็นจูรี่บึงกาฬ</t>
+  </si>
+  <si>
+    <t>M</t>
   </si>
 </sst>
 </file>
@@ -10457,7 +10461,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -10555,6 +10559,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -67114,7 +67121,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04027C31-77F8-4343-AAE9-4D43E616FFDE}">
-  <dimension ref="A1:G288"/>
+  <dimension ref="A1:H288"/>
   <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="10" style="32" bestFit="1" customWidth="1"/>
@@ -67123,10 +67130,11 @@
     <col min="4" max="4" width="11.6328125" style="35" customWidth="1"/>
     <col min="5" max="5" width="9.08984375" style="35" customWidth="1"/>
     <col min="6" max="7" width="16.6328125" style="35" customWidth="1"/>
-    <col min="8" max="16384" width="8.7265625" style="32"/>
+    <col min="8" max="8" width="8.7265625" style="35"/>
+    <col min="9" max="16384" width="8.7265625" style="32"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="17.5" thickBot="1">
+    <row r="1" spans="1:8" ht="17.5" thickBot="1">
       <c r="A1" s="25" t="s">
         <v>234</v>
       </c>
@@ -67148,8 +67156,11 @@
       <c r="G1" s="33" t="s">
         <v>3192</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H1" s="35" t="s">
+        <v>3211</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="17.5" thickBot="1">
       <c r="A2" s="27" t="s">
         <v>2905</v>
       </c>
@@ -67168,15 +67179,19 @@
         <v>3</v>
       </c>
       <c r="F2" s="34">
-        <f>IF(D2&gt;=3,9,0)</f>
+        <f>IF(AND(H2=1,D2&gt;=2),9,IF(D2&gt;=3,9,0))</f>
         <v>9</v>
       </c>
       <c r="G2" s="34">
-        <f>IF(E2&gt;3,3,E2)</f>
+        <f>IF(AND(H2=1,E2&gt;=2),3,IF(E2&gt;3,3,E2))</f>
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H2" s="39">
+        <f t="shared" ref="H2:H65" si="0">IF(ISNUMBER(SEARCH("M", C2)), 1, 0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="17.5" thickBot="1">
       <c r="A3" s="27" t="s">
         <v>2905</v>
       </c>
@@ -67195,15 +67210,19 @@
         <v>4</v>
       </c>
       <c r="F3" s="34">
-        <f t="shared" ref="F3:F66" si="0">IF(D3&gt;=3,9,0)</f>
+        <f t="shared" ref="F3:F66" si="1">IF(AND(H3=1,D3&gt;=2),9,IF(D3&gt;=3,9,0))</f>
         <v>9</v>
       </c>
       <c r="G3" s="34">
-        <f t="shared" ref="G3:G66" si="1">IF(E3&gt;3,3,E3)</f>
+        <f t="shared" ref="G3:G66" si="2">IF(AND(H3=1,E3&gt;=2),3,IF(E3&gt;3,3,E3))</f>
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H3" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="17.5" thickBot="1">
       <c r="A4" s="27" t="s">
         <v>2905</v>
       </c>
@@ -67222,15 +67241,19 @@
         <v>5</v>
       </c>
       <c r="F4" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G4" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H4" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G4" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="17.5" thickBot="1">
       <c r="A5" s="27" t="s">
         <v>2905</v>
       </c>
@@ -67249,15 +67272,19 @@
         <v>3</v>
       </c>
       <c r="F5" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G5" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H5" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G5" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="17.5" thickBot="1">
       <c r="A6" s="27" t="s">
         <v>2905</v>
       </c>
@@ -67276,15 +67303,19 @@
         <v>6</v>
       </c>
       <c r="F6" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G6" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H6" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G6" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="17.5" thickBot="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="17.5" thickBot="1">
       <c r="A7" s="27" t="s">
         <v>2905</v>
       </c>
@@ -67303,15 +67334,19 @@
         <v>4</v>
       </c>
       <c r="F7" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G7" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H7" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G7" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="17.5" thickBot="1">
       <c r="A8" s="27" t="s">
         <v>2905</v>
       </c>
@@ -67330,15 +67365,19 @@
         <v>3</v>
       </c>
       <c r="F8" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G8" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H8" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G8" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="17.5" thickBot="1">
       <c r="A9" s="27" t="s">
         <v>2905</v>
       </c>
@@ -67357,15 +67396,19 @@
         <v>4</v>
       </c>
       <c r="F9" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G9" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H9" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G9" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="17.5" thickBot="1">
       <c r="A10" s="27" t="s">
         <v>2905</v>
       </c>
@@ -67384,15 +67427,19 @@
         <v>1</v>
       </c>
       <c r="F10" s="34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G10" s="34">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="H10" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G10" s="34">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="17.5" thickBot="1">
+    </row>
+    <row r="11" spans="1:8" ht="17.5" thickBot="1">
       <c r="A11" s="27" t="s">
         <v>2905</v>
       </c>
@@ -67411,15 +67458,19 @@
         <v>3</v>
       </c>
       <c r="F11" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G11" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H11" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G11" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="17.5" thickBot="1">
       <c r="A12" s="27" t="s">
         <v>2905</v>
       </c>
@@ -67438,15 +67489,19 @@
         <v>3</v>
       </c>
       <c r="F12" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G12" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H12" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G12" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="17.5" thickBot="1">
       <c r="A13" s="27" t="s">
         <v>2905</v>
       </c>
@@ -67465,15 +67520,19 @@
         <v>3</v>
       </c>
       <c r="F13" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G13" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H13" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G13" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="17.5" thickBot="1">
       <c r="A14" s="27" t="s">
         <v>2905</v>
       </c>
@@ -67492,15 +67551,19 @@
         <v>3</v>
       </c>
       <c r="F14" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G14" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H14" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G14" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="17.5" thickBot="1">
       <c r="A15" s="27" t="s">
         <v>2905</v>
       </c>
@@ -67519,15 +67582,19 @@
         <v>3</v>
       </c>
       <c r="F15" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G15" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H15" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G15" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="17.5" thickBot="1">
       <c r="A16" s="27" t="s">
         <v>2905</v>
       </c>
@@ -67546,15 +67613,19 @@
         <v>3</v>
       </c>
       <c r="F16" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G16" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H16" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G16" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="17.5" thickBot="1">
       <c r="A17" s="27" t="s">
         <v>2905</v>
       </c>
@@ -67573,15 +67644,19 @@
         <v>3</v>
       </c>
       <c r="F17" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G17" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H17" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G17" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="17.5" thickBot="1">
       <c r="A18" s="27" t="s">
         <v>2905</v>
       </c>
@@ -67600,15 +67675,19 @@
         <v>3</v>
       </c>
       <c r="F18" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G18" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H18" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G18" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="17.5" thickBot="1">
       <c r="A19" s="27" t="s">
         <v>2905</v>
       </c>
@@ -67627,15 +67706,19 @@
         <v>4</v>
       </c>
       <c r="F19" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G19" s="34">
+        <f>IF(AND(H19=1,E19&gt;=2),3,IF(E19&gt;3,3,E19))</f>
+        <v>3</v>
+      </c>
+      <c r="H19" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G19" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="17.5" thickBot="1">
       <c r="A20" s="27" t="s">
         <v>2905</v>
       </c>
@@ -67654,15 +67737,19 @@
         <v>3</v>
       </c>
       <c r="F20" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G20" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H20" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G20" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="17.5" thickBot="1">
       <c r="A21" s="27" t="s">
         <v>2905</v>
       </c>
@@ -67681,15 +67768,19 @@
         <v>3</v>
       </c>
       <c r="F21" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G21" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H21" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G21" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="17.5" thickBot="1">
       <c r="A22" s="27" t="s">
         <v>2905</v>
       </c>
@@ -67708,15 +67799,19 @@
         <v>1</v>
       </c>
       <c r="F22" s="34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="34">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="H22" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G22" s="34">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="17.5" thickBot="1">
+    </row>
+    <row r="23" spans="1:8" ht="17.5" thickBot="1">
       <c r="A23" s="27" t="s">
         <v>2905</v>
       </c>
@@ -67735,15 +67830,19 @@
         <v>3</v>
       </c>
       <c r="F23" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G23" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H23" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G23" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="17.5" thickBot="1">
       <c r="A24" s="27" t="s">
         <v>2905</v>
       </c>
@@ -67762,15 +67861,19 @@
         <v>5</v>
       </c>
       <c r="F24" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G24" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H24" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G24" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="17.5" thickBot="1">
       <c r="A25" s="27" t="s">
         <v>2905</v>
       </c>
@@ -67789,15 +67892,19 @@
         <v>4</v>
       </c>
       <c r="F25" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G25" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H25" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G25" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="17.5" thickBot="1">
       <c r="A26" s="27" t="s">
         <v>2905</v>
       </c>
@@ -67816,15 +67923,19 @@
         <v>4</v>
       </c>
       <c r="F26" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G26" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H26" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G26" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="17.5" thickBot="1">
       <c r="A27" s="27" t="s">
         <v>2905</v>
       </c>
@@ -67843,15 +67954,19 @@
         <v>3</v>
       </c>
       <c r="F27" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G27" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H27" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G27" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="17.5" thickBot="1">
       <c r="A28" s="27" t="s">
         <v>2905</v>
       </c>
@@ -67870,15 +67985,19 @@
         <v>4</v>
       </c>
       <c r="F28" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G28" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H28" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G28" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="17.5" thickBot="1">
       <c r="A29" s="27" t="s">
         <v>2905</v>
       </c>
@@ -67897,15 +68016,19 @@
         <v>4</v>
       </c>
       <c r="F29" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G29" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H29" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G29" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="17.5" thickBot="1">
       <c r="A30" s="27" t="s">
         <v>2905</v>
       </c>
@@ -67924,15 +68047,19 @@
         <v>3</v>
       </c>
       <c r="F30" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G30" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H30" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G30" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="17.5" thickBot="1">
       <c r="A31" s="27" t="s">
         <v>2905</v>
       </c>
@@ -67951,15 +68078,19 @@
         <v>4</v>
       </c>
       <c r="F31" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G31" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H31" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G31" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="17.5" thickBot="1">
       <c r="A32" s="27" t="s">
         <v>2905</v>
       </c>
@@ -67978,15 +68109,19 @@
         <v>3</v>
       </c>
       <c r="F32" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G32" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H32" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G32" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="17.5" thickBot="1">
       <c r="A33" s="27" t="s">
         <v>2905</v>
       </c>
@@ -68005,15 +68140,19 @@
         <v>3</v>
       </c>
       <c r="F33" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G33" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H33" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G33" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="17.5" thickBot="1">
       <c r="A34" s="27" t="s">
         <v>2905</v>
       </c>
@@ -68032,15 +68171,19 @@
         <v>5</v>
       </c>
       <c r="F34" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G34" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H34" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G34" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="17.5" thickBot="1">
       <c r="A35" s="27" t="s">
         <v>2905</v>
       </c>
@@ -68059,15 +68202,19 @@
         <v>2</v>
       </c>
       <c r="F35" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G35" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H35" s="39">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G35" s="34">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="17.5" thickBot="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="17.5" thickBot="1">
       <c r="A36" s="27" t="s">
         <v>2905</v>
       </c>
@@ -68086,15 +68233,19 @@
         <v>1</v>
       </c>
       <c r="F36" s="34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G36" s="34">
+        <f>IF(AND(H36=1,E36&gt;=2),3,IF(E36&gt;3,3,E36))</f>
+        <v>1</v>
+      </c>
+      <c r="H36" s="39">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G36" s="34">
-        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="17.5" thickBot="1">
+    <row r="37" spans="1:8" ht="17.5" thickBot="1">
       <c r="A37" s="27" t="s">
         <v>2905</v>
       </c>
@@ -68113,15 +68264,19 @@
         <v>3</v>
       </c>
       <c r="F37" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G37" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H37" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G37" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="17.5" thickBot="1">
       <c r="A38" s="27" t="s">
         <v>2905</v>
       </c>
@@ -68140,15 +68295,19 @@
         <v>2</v>
       </c>
       <c r="F38" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G38" s="34">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="H38" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G38" s="34">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="17.5" thickBot="1">
       <c r="A39" s="27" t="s">
         <v>2905</v>
       </c>
@@ -68167,15 +68326,19 @@
         <v>2</v>
       </c>
       <c r="F39" s="34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G39" s="34">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="H39" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G39" s="34">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="17.5" thickBot="1">
+    </row>
+    <row r="40" spans="1:8" ht="17.5" thickBot="1">
       <c r="A40" s="27" t="s">
         <v>2905</v>
       </c>
@@ -68194,15 +68357,19 @@
         <v>3</v>
       </c>
       <c r="F40" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G40" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H40" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G40" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="17.5" thickBot="1">
       <c r="A41" s="27" t="s">
         <v>2905</v>
       </c>
@@ -68221,15 +68388,19 @@
         <v>1</v>
       </c>
       <c r="F41" s="34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G41" s="34">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="H41" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G41" s="34">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="17.5" thickBot="1">
+    </row>
+    <row r="42" spans="1:8" ht="17.5" thickBot="1">
       <c r="A42" s="27" t="s">
         <v>2905</v>
       </c>
@@ -68248,15 +68419,19 @@
         <v>2</v>
       </c>
       <c r="F42" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G42" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H42" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G42" s="34">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="17.5" thickBot="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="17.5" thickBot="1">
       <c r="A43" s="27" t="s">
         <v>2905</v>
       </c>
@@ -68275,15 +68450,19 @@
         <v>4</v>
       </c>
       <c r="F43" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G43" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H43" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G43" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="17.5" thickBot="1">
       <c r="A44" s="27" t="s">
         <v>2905</v>
       </c>
@@ -68302,15 +68481,19 @@
         <v>3</v>
       </c>
       <c r="F44" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G44" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H44" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G44" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="17.5" thickBot="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="17.5" thickBot="1">
       <c r="A45" s="27" t="s">
         <v>2905</v>
       </c>
@@ -68329,15 +68512,19 @@
         <v>3</v>
       </c>
       <c r="F45" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G45" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H45" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G45" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="17.5" thickBot="1">
       <c r="A46" s="27" t="s">
         <v>2905</v>
       </c>
@@ -68356,15 +68543,19 @@
         <v>3</v>
       </c>
       <c r="F46" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G46" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H46" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G46" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="17.5" thickBot="1">
       <c r="A47" s="27" t="s">
         <v>2905</v>
       </c>
@@ -68383,15 +68574,19 @@
         <v>4</v>
       </c>
       <c r="F47" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G47" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H47" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G47" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="17.5" thickBot="1">
       <c r="A48" s="27" t="s">
         <v>2905</v>
       </c>
@@ -68410,15 +68605,19 @@
         <v>4</v>
       </c>
       <c r="F48" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G48" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H48" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G48" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="17.5" thickBot="1">
       <c r="A49" s="27" t="s">
         <v>2905</v>
       </c>
@@ -68437,15 +68636,19 @@
         <v>3</v>
       </c>
       <c r="F49" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G49" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H49" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G49" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="17.5" thickBot="1">
       <c r="A50" s="27" t="s">
         <v>2905</v>
       </c>
@@ -68464,15 +68667,19 @@
         <v>2</v>
       </c>
       <c r="F50" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G50" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H50" s="39">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G50" s="34">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="17.5" thickBot="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="17.5" thickBot="1">
       <c r="A51" s="27" t="s">
         <v>2905</v>
       </c>
@@ -68491,15 +68698,19 @@
         <v>2</v>
       </c>
       <c r="F51" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G51" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H51" s="39">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G51" s="34">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="17.5" thickBot="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="17.5" thickBot="1">
       <c r="A52" s="27" t="s">
         <v>2905</v>
       </c>
@@ -68518,15 +68729,19 @@
         <v>4</v>
       </c>
       <c r="F52" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G52" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H52" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G52" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="17.5" thickBot="1">
       <c r="A53" s="27" t="s">
         <v>2905</v>
       </c>
@@ -68545,15 +68760,19 @@
         <v>2</v>
       </c>
       <c r="F53" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G53" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H53" s="39">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G53" s="34">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="17.5" thickBot="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="17.5" thickBot="1">
       <c r="A54" s="27" t="s">
         <v>2905</v>
       </c>
@@ -68572,15 +68791,19 @@
         <v>2</v>
       </c>
       <c r="F54" s="34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G54" s="34">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="H54" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G54" s="34">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="17.5" thickBot="1">
+    </row>
+    <row r="55" spans="1:8" ht="17.5" thickBot="1">
       <c r="A55" s="27" t="s">
         <v>2905</v>
       </c>
@@ -68599,15 +68822,19 @@
         <v>2</v>
       </c>
       <c r="F55" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G55" s="34">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="H55" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G55" s="34">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="17.5" thickBot="1">
       <c r="A56" s="27" t="s">
         <v>2905</v>
       </c>
@@ -68626,15 +68853,19 @@
         <v>0</v>
       </c>
       <c r="F56" s="34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G56" s="34">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H56" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G56" s="34">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="17.5" thickBot="1">
+    </row>
+    <row r="57" spans="1:8" ht="17.5" thickBot="1">
       <c r="A57" s="27" t="s">
         <v>2905</v>
       </c>
@@ -68653,15 +68884,19 @@
         <v>2</v>
       </c>
       <c r="F57" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G57" s="34">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="H57" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G57" s="34">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="17.5" thickBot="1">
       <c r="A58" s="27" t="s">
         <v>2905</v>
       </c>
@@ -68680,15 +68915,19 @@
         <v>2</v>
       </c>
       <c r="F58" s="34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G58" s="34">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="H58" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G58" s="34">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="17.5" thickBot="1">
+    </row>
+    <row r="59" spans="1:8" ht="17.5" thickBot="1">
       <c r="A59" s="27" t="s">
         <v>2905</v>
       </c>
@@ -68707,15 +68946,19 @@
         <v>3</v>
       </c>
       <c r="F59" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G59" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H59" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G59" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="17.5" thickBot="1">
       <c r="A60" s="27" t="s">
         <v>2905</v>
       </c>
@@ -68734,15 +68977,19 @@
         <v>2</v>
       </c>
       <c r="F60" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G60" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H60" s="39">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G60" s="34">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="17.5" thickBot="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="17.5" thickBot="1">
       <c r="A61" s="27" t="s">
         <v>2905</v>
       </c>
@@ -68761,15 +69008,19 @@
         <v>2</v>
       </c>
       <c r="F61" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G61" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H61" s="39">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G61" s="34">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="17.5" thickBot="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="17.5" thickBot="1">
       <c r="A62" s="27" t="s">
         <v>2905</v>
       </c>
@@ -68788,15 +69039,19 @@
         <v>5</v>
       </c>
       <c r="F62" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G62" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H62" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G62" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="17.5" thickBot="1">
       <c r="A63" s="27" t="s">
         <v>2905</v>
       </c>
@@ -68815,15 +69070,19 @@
         <v>3</v>
       </c>
       <c r="F63" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G63" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H63" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G63" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="17.5" thickBot="1">
       <c r="A64" s="27" t="s">
         <v>2905</v>
       </c>
@@ -68842,15 +69101,19 @@
         <v>2</v>
       </c>
       <c r="F64" s="34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G64" s="34">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="H64" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G64" s="34">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="17.5" thickBot="1">
+    </row>
+    <row r="65" spans="1:8" ht="17.5" thickBot="1">
       <c r="A65" s="27" t="s">
         <v>2905</v>
       </c>
@@ -68869,15 +69132,19 @@
         <v>4</v>
       </c>
       <c r="F65" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G65" s="34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H65" s="39">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G65" s="34">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="17.5" thickBot="1">
       <c r="A66" s="27" t="s">
         <v>2905</v>
       </c>
@@ -68896,15 +69163,19 @@
         <v>4</v>
       </c>
       <c r="F66" s="34">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="G66" s="34">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H66" s="39">
+        <f t="shared" ref="H66:H129" si="3">IF(ISNUMBER(SEARCH("M", C66)), 1, 0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="17.5" thickBot="1">
       <c r="A67" s="27" t="s">
         <v>2905</v>
       </c>
@@ -68923,15 +69194,19 @@
         <v>2</v>
       </c>
       <c r="F67" s="34">
-        <f t="shared" ref="F67:F130" si="2">IF(D67&gt;=3,9,0)</f>
+        <f t="shared" ref="F67:F130" si="4">IF(AND(H67=1,D67&gt;=2),9,IF(D67&gt;=3,9,0))</f>
         <v>0</v>
       </c>
       <c r="G67" s="34">
-        <f t="shared" ref="G67:G130" si="3">IF(E67&gt;3,3,E67)</f>
+        <f t="shared" ref="G67:G130" si="5">IF(AND(H67=1,E67&gt;=2),3,IF(E67&gt;3,3,E67))</f>
         <v>2</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H67" s="39">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="17.5" thickBot="1">
       <c r="A68" s="27" t="s">
         <v>2905</v>
       </c>
@@ -68950,15 +69225,19 @@
         <v>3</v>
       </c>
       <c r="F68" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G68" s="34">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="H68" s="39">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="17.5" thickBot="1">
       <c r="A69" s="27" t="s">
         <v>2905</v>
       </c>
@@ -68977,15 +69256,19 @@
         <v>3</v>
       </c>
       <c r="F69" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G69" s="34">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="H69" s="39">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="17.5" thickBot="1">
       <c r="A70" s="27" t="s">
         <v>2905</v>
       </c>
@@ -69004,15 +69287,19 @@
         <v>3</v>
       </c>
       <c r="F70" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G70" s="34">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="H70" s="39">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="17.5" thickBot="1">
       <c r="A71" s="27" t="s">
         <v>2905</v>
       </c>
@@ -69031,15 +69318,19 @@
         <v>0</v>
       </c>
       <c r="F71" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G71" s="34">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H71" s="39">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="17.5" thickBot="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="17.5" thickBot="1">
       <c r="A72" s="27" t="s">
         <v>2905</v>
       </c>
@@ -69058,15 +69349,19 @@
         <v>3</v>
       </c>
       <c r="F72" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G72" s="34">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="H72" s="39">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="17.5" thickBot="1">
       <c r="A73" s="27" t="s">
         <v>2975</v>
       </c>
@@ -69085,15 +69380,19 @@
         <v>1</v>
       </c>
       <c r="F73" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G73" s="34">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="H73" s="39">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="17.5" thickBot="1">
       <c r="A74" s="27" t="s">
         <v>2975</v>
       </c>
@@ -69112,15 +69411,19 @@
         <v>0</v>
       </c>
       <c r="F74" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G74" s="34">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H74" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="17.5" thickBot="1">
+    <row r="75" spans="1:8" ht="17.5" thickBot="1">
       <c r="A75" s="27" t="s">
         <v>2975</v>
       </c>
@@ -69139,15 +69442,19 @@
         <v>2</v>
       </c>
       <c r="F75" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G75" s="34">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H75" s="39">
         <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="17.5" thickBot="1">
       <c r="A76" s="27" t="s">
         <v>2975</v>
       </c>
@@ -69166,15 +69473,19 @@
         <v>0</v>
       </c>
       <c r="F76" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G76" s="34">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H76" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="17.5" thickBot="1">
+    <row r="77" spans="1:8" ht="17.5" thickBot="1">
       <c r="A77" s="27" t="s">
         <v>2975</v>
       </c>
@@ -69193,15 +69504,19 @@
         <v>1</v>
       </c>
       <c r="F77" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G77" s="34">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="H77" s="39">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="17.5" thickBot="1">
       <c r="A78" s="27" t="s">
         <v>2975</v>
       </c>
@@ -69220,15 +69535,19 @@
         <v>2</v>
       </c>
       <c r="F78" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G78" s="34">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H78" s="39">
         <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="17.5" thickBot="1">
       <c r="A79" s="27" t="s">
         <v>2975</v>
       </c>
@@ -69247,15 +69566,19 @@
         <v>0</v>
       </c>
       <c r="F79" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G79" s="34">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H79" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="17.5" thickBot="1">
+    <row r="80" spans="1:8" ht="17.5" thickBot="1">
       <c r="A80" s="27" t="s">
         <v>2975</v>
       </c>
@@ -69274,15 +69597,19 @@
         <v>0</v>
       </c>
       <c r="F80" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G80" s="34">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H80" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="17.5" thickBot="1">
+    <row r="81" spans="1:8" ht="17.5" thickBot="1">
       <c r="A81" s="27" t="s">
         <v>2975</v>
       </c>
@@ -69301,15 +69628,19 @@
         <v>3</v>
       </c>
       <c r="F81" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G81" s="34">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="H81" s="39">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="17.5" thickBot="1">
       <c r="A82" s="27" t="s">
         <v>2975</v>
       </c>
@@ -69328,15 +69659,19 @@
         <v>1</v>
       </c>
       <c r="F82" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G82" s="34">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="H82" s="39">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="17.5" thickBot="1">
       <c r="A83" s="27" t="e">
         <v>#N/A</v>
       </c>
@@ -69355,15 +69690,19 @@
         <v>3</v>
       </c>
       <c r="F83" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G83" s="34">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="H83" s="39">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="17.5" thickBot="1">
       <c r="A84" s="27" t="s">
         <v>2975</v>
       </c>
@@ -69382,15 +69721,19 @@
         <v>3</v>
       </c>
       <c r="F84" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G84" s="34">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="H84" s="39">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" ht="17.5" thickBot="1">
       <c r="A85" s="27" t="s">
         <v>2975</v>
       </c>
@@ -69409,15 +69752,19 @@
         <v>2</v>
       </c>
       <c r="F85" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G85" s="34">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H85" s="39">
         <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="17.5" thickBot="1">
       <c r="A86" s="27" t="s">
         <v>2975</v>
       </c>
@@ -69436,15 +69783,19 @@
         <v>3</v>
       </c>
       <c r="F86" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G86" s="34">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="H86" s="39">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" ht="17.5" thickBot="1">
       <c r="A87" s="27" t="s">
         <v>2975</v>
       </c>
@@ -69463,15 +69814,19 @@
         <v>3</v>
       </c>
       <c r="F87" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G87" s="34">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="H87" s="39">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" ht="17.5" thickBot="1">
       <c r="A88" s="27" t="s">
         <v>2975</v>
       </c>
@@ -69490,15 +69845,19 @@
         <v>3</v>
       </c>
       <c r="F88" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G88" s="34">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="H88" s="39">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" ht="17.5" thickBot="1">
       <c r="A89" s="27" t="s">
         <v>2975</v>
       </c>
@@ -69517,15 +69876,19 @@
         <v>0</v>
       </c>
       <c r="F89" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G89" s="34">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H89" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="17.5" thickBot="1">
+    <row r="90" spans="1:8" ht="17.5" thickBot="1">
       <c r="A90" s="27" t="s">
         <v>2975</v>
       </c>
@@ -69544,15 +69907,19 @@
         <v>3</v>
       </c>
       <c r="F90" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G90" s="34">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="H90" s="39">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" ht="17.5" thickBot="1">
       <c r="A91" s="27" t="s">
         <v>2975</v>
       </c>
@@ -69571,15 +69938,19 @@
         <v>4</v>
       </c>
       <c r="F91" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G91" s="34">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="H91" s="39">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" ht="17.5" thickBot="1">
       <c r="A92" s="27" t="s">
         <v>2975</v>
       </c>
@@ -69598,15 +69969,19 @@
         <v>2</v>
       </c>
       <c r="F92" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G92" s="34">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H92" s="39">
         <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" ht="17.5" thickBot="1">
       <c r="A93" s="27" t="s">
         <v>2975</v>
       </c>
@@ -69625,15 +70000,19 @@
         <v>2</v>
       </c>
       <c r="F93" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G93" s="34">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H93" s="39">
         <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" ht="17.5" thickBot="1">
       <c r="A94" s="27" t="s">
         <v>2975</v>
       </c>
@@ -69652,15 +70031,19 @@
         <v>1</v>
       </c>
       <c r="F94" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G94" s="34">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="H94" s="39">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="17.5" thickBot="1">
       <c r="A95" s="27" t="s">
         <v>2975</v>
       </c>
@@ -69679,15 +70062,19 @@
         <v>1</v>
       </c>
       <c r="F95" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G95" s="34">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="H95" s="39">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" ht="17.5" thickBot="1">
       <c r="A96" s="27" t="s">
         <v>2975</v>
       </c>
@@ -69706,15 +70093,19 @@
         <v>3</v>
       </c>
       <c r="F96" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G96" s="34">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="H96" s="39">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" ht="17.5" thickBot="1">
       <c r="A97" s="27" t="s">
         <v>2975</v>
       </c>
@@ -69733,15 +70124,19 @@
         <v>3</v>
       </c>
       <c r="F97" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G97" s="34">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="H97" s="39">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" ht="17.5" thickBot="1">
       <c r="A98" s="27" t="s">
         <v>2975</v>
       </c>
@@ -69760,15 +70155,19 @@
         <v>3</v>
       </c>
       <c r="F98" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G98" s="34">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="H98" s="39">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" ht="17.5" thickBot="1">
       <c r="A99" s="27" t="s">
         <v>2975</v>
       </c>
@@ -69787,15 +70186,19 @@
         <v>3</v>
       </c>
       <c r="F99" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G99" s="34">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="H99" s="39">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" ht="17.5" thickBot="1">
       <c r="A100" s="27" t="s">
         <v>2975</v>
       </c>
@@ -69814,15 +70217,19 @@
         <v>2</v>
       </c>
       <c r="F100" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G100" s="34">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H100" s="39">
         <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" ht="17.5" thickBot="1">
       <c r="A101" s="27" t="s">
         <v>2975</v>
       </c>
@@ -69841,15 +70248,19 @@
         <v>3</v>
       </c>
       <c r="F101" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G101" s="34">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="H101" s="39">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" ht="17.5" thickBot="1">
       <c r="A102" s="27" t="s">
         <v>2975</v>
       </c>
@@ -69868,15 +70279,19 @@
         <v>2</v>
       </c>
       <c r="F102" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G102" s="34">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H102" s="39">
         <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" ht="17.5" thickBot="1">
       <c r="A103" s="27" t="s">
         <v>2975</v>
       </c>
@@ -69895,15 +70310,19 @@
         <v>0</v>
       </c>
       <c r="F103" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G103" s="34">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H103" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="17.5" thickBot="1">
+    <row r="104" spans="1:8" ht="17.5" thickBot="1">
       <c r="A104" s="27" t="s">
         <v>2975</v>
       </c>
@@ -69922,15 +70341,19 @@
         <v>3</v>
       </c>
       <c r="F104" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G104" s="34">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="H104" s="39">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" ht="17.5" thickBot="1">
       <c r="A105" s="27" t="s">
         <v>2975</v>
       </c>
@@ -69949,15 +70372,19 @@
         <v>1</v>
       </c>
       <c r="F105" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G105" s="34">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="H105" s="39">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" ht="17.5" thickBot="1">
       <c r="A106" s="27" t="s">
         <v>2975</v>
       </c>
@@ -69976,15 +70403,19 @@
         <v>2</v>
       </c>
       <c r="F106" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G106" s="34">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H106" s="39">
         <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" ht="17.5" thickBot="1">
       <c r="A107" s="27" t="s">
         <v>2975</v>
       </c>
@@ -70003,15 +70434,19 @@
         <v>2</v>
       </c>
       <c r="F107" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G107" s="34">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H107" s="39">
         <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" ht="17.5" thickBot="1">
       <c r="A108" s="27" t="s">
         <v>2975</v>
       </c>
@@ -70030,15 +70465,19 @@
         <v>0</v>
       </c>
       <c r="F108" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G108" s="34">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H108" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="17.5" thickBot="1">
+    <row r="109" spans="1:8" ht="17.5" thickBot="1">
       <c r="A109" s="27" t="s">
         <v>2975</v>
       </c>
@@ -70057,15 +70496,19 @@
         <v>2</v>
       </c>
       <c r="F109" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G109" s="34">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H109" s="39">
         <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" ht="17.5" thickBot="1">
       <c r="A110" s="27" t="s">
         <v>2975</v>
       </c>
@@ -70084,15 +70527,19 @@
         <v>5</v>
       </c>
       <c r="F110" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G110" s="34">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="H110" s="39">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" ht="17.5" thickBot="1">
       <c r="A111" s="27" t="s">
         <v>2975</v>
       </c>
@@ -70111,15 +70558,19 @@
         <v>0</v>
       </c>
       <c r="F111" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G111" s="34">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H111" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="17.5" thickBot="1">
+    <row r="112" spans="1:8" ht="17.5" thickBot="1">
       <c r="A112" s="27" t="s">
         <v>2975</v>
       </c>
@@ -70138,15 +70589,19 @@
         <v>0</v>
       </c>
       <c r="F112" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G112" s="34">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H112" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:7" ht="17.5" thickBot="1">
+    <row r="113" spans="1:8" ht="17.5" thickBot="1">
       <c r="A113" s="27" t="s">
         <v>2884</v>
       </c>
@@ -70165,15 +70620,19 @@
         <v>3</v>
       </c>
       <c r="F113" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G113" s="34">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="H113" s="39">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" ht="17.5" thickBot="1">
       <c r="A114" s="27" t="s">
         <v>2884</v>
       </c>
@@ -70192,15 +70651,19 @@
         <v>3</v>
       </c>
       <c r="F114" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G114" s="34">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="H114" s="39">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" ht="17.5" thickBot="1">
       <c r="A115" s="27" t="s">
         <v>2884</v>
       </c>
@@ -70219,15 +70682,19 @@
         <v>1</v>
       </c>
       <c r="F115" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G115" s="34">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="H115" s="39">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" ht="17.5" thickBot="1">
       <c r="A116" s="27" t="s">
         <v>2884</v>
       </c>
@@ -70246,15 +70713,19 @@
         <v>3</v>
       </c>
       <c r="F116" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G116" s="34">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="H116" s="39">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" ht="17.5" thickBot="1">
       <c r="A117" s="27" t="s">
         <v>2900</v>
       </c>
@@ -70273,15 +70744,19 @@
         <v>3</v>
       </c>
       <c r="F117" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G117" s="34">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="H117" s="39">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" ht="17.5" thickBot="1">
       <c r="A118" s="27" t="s">
         <v>2900</v>
       </c>
@@ -70300,15 +70775,19 @@
         <v>5</v>
       </c>
       <c r="F118" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G118" s="34">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="H118" s="39">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" ht="17.5" thickBot="1">
       <c r="A119" s="27" t="s">
         <v>2900</v>
       </c>
@@ -70327,15 +70806,19 @@
         <v>2</v>
       </c>
       <c r="F119" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G119" s="34">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H119" s="39">
         <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" ht="17.5" thickBot="1">
       <c r="A120" s="27" t="s">
         <v>2900</v>
       </c>
@@ -70354,15 +70837,19 @@
         <v>3</v>
       </c>
       <c r="F120" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G120" s="34">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="H120" s="39">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" ht="17.5" thickBot="1">
       <c r="A121" s="27" t="s">
         <v>2900</v>
       </c>
@@ -70381,15 +70868,19 @@
         <v>2</v>
       </c>
       <c r="F121" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G121" s="34">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H121" s="39">
         <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" ht="17.5" thickBot="1">
       <c r="A122" s="27" t="s">
         <v>2900</v>
       </c>
@@ -70408,15 +70899,19 @@
         <v>3</v>
       </c>
       <c r="F122" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G122" s="34">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="H122" s="39">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" ht="17.5" thickBot="1">
       <c r="A123" s="27" t="s">
         <v>2900</v>
       </c>
@@ -70435,15 +70930,19 @@
         <v>1</v>
       </c>
       <c r="F123" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G123" s="34">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="H123" s="39">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" ht="17.5" thickBot="1">
       <c r="A124" s="27" t="s">
         <v>2900</v>
       </c>
@@ -70462,15 +70961,19 @@
         <v>3</v>
       </c>
       <c r="F124" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G124" s="34">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="H124" s="39">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" ht="17.5" thickBot="1">
       <c r="A125" s="27" t="s">
         <v>2900</v>
       </c>
@@ -70489,15 +70992,19 @@
         <v>3</v>
       </c>
       <c r="F125" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G125" s="34">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="H125" s="39">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" ht="17.5" thickBot="1">
       <c r="A126" s="27" t="s">
         <v>2900</v>
       </c>
@@ -70516,15 +71023,19 @@
         <v>4</v>
       </c>
       <c r="F126" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G126" s="34">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="H126" s="39">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" ht="17.5" thickBot="1">
       <c r="A127" s="27" t="s">
         <v>2900</v>
       </c>
@@ -70543,15 +71054,19 @@
         <v>4</v>
       </c>
       <c r="F127" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G127" s="34">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="H127" s="39">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" ht="17.5" thickBot="1">
       <c r="A128" s="27" t="s">
         <v>2900</v>
       </c>
@@ -70570,15 +71085,19 @@
         <v>0</v>
       </c>
       <c r="F128" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G128" s="34">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H128" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="17.5" thickBot="1">
+    <row r="129" spans="1:8" ht="17.5" thickBot="1">
       <c r="A129" s="27" t="s">
         <v>2900</v>
       </c>
@@ -70597,15 +71116,19 @@
         <v>3</v>
       </c>
       <c r="F129" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G129" s="34">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="H129" s="39">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" ht="17.5" thickBot="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" ht="17.5" thickBot="1">
       <c r="A130" s="27" t="s">
         <v>2900</v>
       </c>
@@ -70624,15 +71147,19 @@
         <v>3</v>
       </c>
       <c r="F130" s="34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G130" s="34">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="131" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H130" s="39">
+        <f t="shared" ref="H130:H193" si="6">IF(ISNUMBER(SEARCH("M", C130)), 1, 0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" ht="17.5" thickBot="1">
       <c r="A131" s="27" t="s">
         <v>2900</v>
       </c>
@@ -70651,15 +71178,19 @@
         <v>3</v>
       </c>
       <c r="F131" s="34">
-        <f t="shared" ref="F131:F194" si="4">IF(D131&gt;=3,9,0)</f>
+        <f t="shared" ref="F131:F194" si="7">IF(AND(H131=1,D131&gt;=2),9,IF(D131&gt;=3,9,0))</f>
         <v>9</v>
       </c>
       <c r="G131" s="34">
-        <f t="shared" ref="G131:G194" si="5">IF(E131&gt;3,3,E131)</f>
+        <f t="shared" ref="G131:G194" si="8">IF(AND(H131=1,E131&gt;=2),3,IF(E131&gt;3,3,E131))</f>
         <v>3</v>
       </c>
-    </row>
-    <row r="132" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H131" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" ht="17.5" thickBot="1">
       <c r="A132" s="27" t="s">
         <v>2900</v>
       </c>
@@ -70678,15 +71209,19 @@
         <v>3</v>
       </c>
       <c r="F132" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G132" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="133" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H132" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" ht="17.5" thickBot="1">
       <c r="A133" s="27" t="s">
         <v>2900</v>
       </c>
@@ -70705,15 +71240,19 @@
         <v>4</v>
       </c>
       <c r="F133" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G133" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="134" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H133" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" ht="17.5" thickBot="1">
       <c r="A134" s="27" t="s">
         <v>2900</v>
       </c>
@@ -70732,15 +71271,19 @@
         <v>2</v>
       </c>
       <c r="F134" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G134" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="135" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H134" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" ht="17.5" thickBot="1">
       <c r="A135" s="27" t="s">
         <v>2900</v>
       </c>
@@ -70759,15 +71302,19 @@
         <v>2</v>
       </c>
       <c r="F135" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G135" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="136" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H135" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" ht="17.5" thickBot="1">
       <c r="A136" s="27" t="s">
         <v>2900</v>
       </c>
@@ -70786,15 +71333,19 @@
         <v>3</v>
       </c>
       <c r="F136" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G136" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="137" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H136" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" ht="17.5" thickBot="1">
       <c r="A137" s="27" t="s">
         <v>2890</v>
       </c>
@@ -70813,15 +71364,19 @@
         <v>0</v>
       </c>
       <c r="F137" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G137" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="138" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H137" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" ht="17.5" thickBot="1">
       <c r="A138" s="27" t="s">
         <v>2890</v>
       </c>
@@ -70840,15 +71395,19 @@
         <v>0</v>
       </c>
       <c r="F138" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G138" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="139" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H138" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" ht="17.5" thickBot="1">
       <c r="A139" s="27" t="s">
         <v>2890</v>
       </c>
@@ -70867,15 +71426,19 @@
         <v>3</v>
       </c>
       <c r="F139" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G139" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="140" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H139" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" ht="17.5" thickBot="1">
       <c r="A140" s="27" t="s">
         <v>2890</v>
       </c>
@@ -70894,15 +71457,19 @@
         <v>3</v>
       </c>
       <c r="F140" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G140" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="141" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H140" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" ht="17.5" thickBot="1">
       <c r="A141" s="27" t="s">
         <v>2890</v>
       </c>
@@ -70921,15 +71488,19 @@
         <v>4</v>
       </c>
       <c r="F141" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G141" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="142" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H141" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" ht="17.5" thickBot="1">
       <c r="A142" s="27" t="s">
         <v>2890</v>
       </c>
@@ -70948,15 +71519,19 @@
         <v>2</v>
       </c>
       <c r="F142" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G142" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="143" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H142" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" ht="17.5" thickBot="1">
       <c r="A143" s="27" t="s">
         <v>2890</v>
       </c>
@@ -70975,15 +71550,19 @@
         <v>3</v>
       </c>
       <c r="F143" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G143" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="144" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H143" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" ht="17.5" thickBot="1">
       <c r="A144" s="27" t="s">
         <v>2890</v>
       </c>
@@ -71002,15 +71581,19 @@
         <v>5</v>
       </c>
       <c r="F144" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G144" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="145" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H144" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" ht="17.5" thickBot="1">
       <c r="A145" s="27" t="s">
         <v>2890</v>
       </c>
@@ -71029,15 +71612,19 @@
         <v>1</v>
       </c>
       <c r="F145" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G145" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="146" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H145" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" ht="17.5" thickBot="1">
       <c r="A146" s="27" t="s">
         <v>2890</v>
       </c>
@@ -71056,15 +71643,19 @@
         <v>9</v>
       </c>
       <c r="F146" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G146" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="147" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H146" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" ht="17.5" thickBot="1">
       <c r="A147" s="27" t="s">
         <v>2890</v>
       </c>
@@ -71083,15 +71674,19 @@
         <v>2</v>
       </c>
       <c r="F147" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G147" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="148" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H147" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" ht="17.5" thickBot="1">
       <c r="A148" s="27" t="s">
         <v>2890</v>
       </c>
@@ -71110,15 +71705,19 @@
         <v>0</v>
       </c>
       <c r="F148" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G148" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="149" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H148" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" ht="17.5" thickBot="1">
       <c r="A149" s="27" t="s">
         <v>2890</v>
       </c>
@@ -71137,15 +71736,19 @@
         <v>3</v>
       </c>
       <c r="F149" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G149" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="150" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H149" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" ht="17.5" thickBot="1">
       <c r="A150" s="27" t="s">
         <v>2890</v>
       </c>
@@ -71164,15 +71767,19 @@
         <v>2</v>
       </c>
       <c r="F150" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G150" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="151" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H150" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" ht="17.5" thickBot="1">
       <c r="A151" s="27" t="s">
         <v>2890</v>
       </c>
@@ -71191,15 +71798,19 @@
         <v>3</v>
       </c>
       <c r="F151" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G151" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="152" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H151" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" ht="17.5" thickBot="1">
       <c r="A152" s="27" t="s">
         <v>2890</v>
       </c>
@@ -71218,15 +71829,19 @@
         <v>6</v>
       </c>
       <c r="F152" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G152" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="153" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H152" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" ht="17.5" thickBot="1">
       <c r="A153" s="27" t="s">
         <v>2890</v>
       </c>
@@ -71245,15 +71860,19 @@
         <v>5</v>
       </c>
       <c r="F153" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G153" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="154" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H153" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" ht="17.5" thickBot="1">
       <c r="A154" s="27" t="s">
         <v>2890</v>
       </c>
@@ -71272,15 +71891,19 @@
         <v>3</v>
       </c>
       <c r="F154" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G154" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="155" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H154" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" ht="17.5" thickBot="1">
       <c r="A155" s="27" t="s">
         <v>2890</v>
       </c>
@@ -71299,15 +71922,19 @@
         <v>1</v>
       </c>
       <c r="F155" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G155" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="156" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H155" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" ht="17.5" thickBot="1">
       <c r="A156" s="27" t="s">
         <v>2890</v>
       </c>
@@ -71326,15 +71953,19 @@
         <v>3</v>
       </c>
       <c r="F156" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G156" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="157" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H156" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" ht="17.5" thickBot="1">
       <c r="A157" s="27" t="s">
         <v>2890</v>
       </c>
@@ -71353,15 +71984,19 @@
         <v>3</v>
       </c>
       <c r="F157" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G157" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="158" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H157" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" ht="17.5" thickBot="1">
       <c r="A158" s="27" t="s">
         <v>2890</v>
       </c>
@@ -71380,15 +72015,19 @@
         <v>3</v>
       </c>
       <c r="F158" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G158" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="159" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H158" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" ht="17.5" thickBot="1">
       <c r="A159" s="27" t="s">
         <v>2890</v>
       </c>
@@ -71407,15 +72046,19 @@
         <v>3</v>
       </c>
       <c r="F159" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G159" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="160" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H159" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" ht="17.5" thickBot="1">
       <c r="A160" s="27" t="s">
         <v>2890</v>
       </c>
@@ -71434,15 +72077,19 @@
         <v>3</v>
       </c>
       <c r="F160" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G160" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="161" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H160" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" ht="17.5" thickBot="1">
       <c r="A161" s="27" t="s">
         <v>2890</v>
       </c>
@@ -71461,15 +72108,19 @@
         <v>4</v>
       </c>
       <c r="F161" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G161" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="162" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H161" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" ht="17.5" thickBot="1">
       <c r="A162" s="27" t="s">
         <v>2890</v>
       </c>
@@ -71488,15 +72139,19 @@
         <v>3</v>
       </c>
       <c r="F162" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G162" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="163" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H162" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" ht="17.5" thickBot="1">
       <c r="A163" s="27" t="s">
         <v>2890</v>
       </c>
@@ -71515,15 +72170,19 @@
         <v>3</v>
       </c>
       <c r="F163" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G163" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="164" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H163" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" ht="17.5" thickBot="1">
       <c r="A164" s="27" t="s">
         <v>2890</v>
       </c>
@@ -71542,15 +72201,19 @@
         <v>0</v>
       </c>
       <c r="F164" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G164" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="165" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H164" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" ht="17.5" thickBot="1">
       <c r="A165" s="27" t="s">
         <v>2890</v>
       </c>
@@ -71569,15 +72232,19 @@
         <v>3</v>
       </c>
       <c r="F165" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G165" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="166" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H165" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" ht="17.5" thickBot="1">
       <c r="A166" s="27" t="s">
         <v>2890</v>
       </c>
@@ -71596,15 +72263,19 @@
         <v>3</v>
       </c>
       <c r="F166" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G166" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="167" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H166" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" ht="17.5" thickBot="1">
       <c r="A167" s="27" t="s">
         <v>2890</v>
       </c>
@@ -71623,15 +72294,19 @@
         <v>2</v>
       </c>
       <c r="F167" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G167" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="168" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H167" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" ht="17.5" thickBot="1">
       <c r="A168" s="27" t="s">
         <v>2890</v>
       </c>
@@ -71650,15 +72325,19 @@
         <v>3</v>
       </c>
       <c r="F168" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G168" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="169" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H168" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" ht="17.5" thickBot="1">
       <c r="A169" s="27" t="s">
         <v>2890</v>
       </c>
@@ -71677,15 +72356,19 @@
         <v>2</v>
       </c>
       <c r="F169" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G169" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="170" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H169" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" ht="17.5" thickBot="1">
       <c r="A170" s="27" t="s">
         <v>2890</v>
       </c>
@@ -71704,15 +72387,19 @@
         <v>3</v>
       </c>
       <c r="F170" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G170" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="171" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H170" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" ht="17.5" thickBot="1">
       <c r="A171" s="27" t="s">
         <v>2890</v>
       </c>
@@ -71731,15 +72418,19 @@
         <v>3</v>
       </c>
       <c r="F171" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G171" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="172" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H171" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" ht="17.5" thickBot="1">
       <c r="A172" s="27" t="s">
         <v>2890</v>
       </c>
@@ -71758,15 +72449,19 @@
         <v>3</v>
       </c>
       <c r="F172" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G172" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="173" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H172" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" ht="17.5" thickBot="1">
       <c r="A173" s="27" t="s">
         <v>2890</v>
       </c>
@@ -71785,15 +72480,19 @@
         <v>2</v>
       </c>
       <c r="F173" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G173" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="174" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H173" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" ht="17.5" thickBot="1">
       <c r="A174" s="27" t="s">
         <v>2890</v>
       </c>
@@ -71812,15 +72511,19 @@
         <v>3</v>
       </c>
       <c r="F174" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G174" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="175" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H174" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" ht="17.5" thickBot="1">
       <c r="A175" s="27" t="s">
         <v>2890</v>
       </c>
@@ -71839,15 +72542,19 @@
         <v>0</v>
       </c>
       <c r="F175" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G175" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="176" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H175" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" ht="17.5" thickBot="1">
       <c r="A176" s="27" t="s">
         <v>2890</v>
       </c>
@@ -71866,15 +72573,19 @@
         <v>0</v>
       </c>
       <c r="F176" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G176" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="177" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H176" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" ht="17.5" thickBot="1">
       <c r="A177" s="27" t="s">
         <v>3149</v>
       </c>
@@ -71893,15 +72604,19 @@
         <v>0</v>
       </c>
       <c r="F177" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G177" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="178" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H177" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" ht="17.5" thickBot="1">
       <c r="A178" s="27" t="s">
         <v>3149</v>
       </c>
@@ -71920,15 +72635,19 @@
         <v>1</v>
       </c>
       <c r="F178" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G178" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="179" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H178" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" ht="17.5" thickBot="1">
       <c r="A179" s="27" t="s">
         <v>3149</v>
       </c>
@@ -71947,15 +72666,19 @@
         <v>4</v>
       </c>
       <c r="F179" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G179" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="180" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H179" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" ht="17.5" thickBot="1">
       <c r="A180" s="27" t="s">
         <v>3149</v>
       </c>
@@ -71974,15 +72697,19 @@
         <v>3</v>
       </c>
       <c r="F180" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G180" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="181" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H180" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" ht="17.5" thickBot="1">
       <c r="A181" s="27" t="s">
         <v>3149</v>
       </c>
@@ -72001,15 +72728,19 @@
         <v>2</v>
       </c>
       <c r="F181" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G181" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="182" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H181" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" ht="17.5" thickBot="1">
       <c r="A182" s="27" t="s">
         <v>3149</v>
       </c>
@@ -72028,15 +72759,19 @@
         <v>3</v>
       </c>
       <c r="F182" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G182" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="183" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H182" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" ht="17.5" thickBot="1">
       <c r="A183" s="27" t="s">
         <v>3149</v>
       </c>
@@ -72055,15 +72790,19 @@
         <v>3</v>
       </c>
       <c r="F183" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G183" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="184" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H183" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" ht="17.5" thickBot="1">
       <c r="A184" s="27" t="s">
         <v>3149</v>
       </c>
@@ -72082,15 +72821,19 @@
         <v>4</v>
       </c>
       <c r="F184" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G184" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="185" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H184" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" ht="17.5" thickBot="1">
       <c r="A185" s="27" t="s">
         <v>3149</v>
       </c>
@@ -72109,15 +72852,19 @@
         <v>5</v>
       </c>
       <c r="F185" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G185" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="186" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H185" s="39">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" ht="17.5" thickBot="1">
       <c r="A186" s="27" t="s">
         <v>3149</v>
       </c>
@@ -72136,15 +72883,19 @@
         <v>3</v>
       </c>
       <c r="F186" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G186" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="187" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H186" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" ht="17.5" thickBot="1">
       <c r="A187" s="27" t="s">
         <v>3149</v>
       </c>
@@ -72163,15 +72914,19 @@
         <v>3</v>
       </c>
       <c r="F187" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G187" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="188" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H187" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" ht="17.5" thickBot="1">
       <c r="A188" s="27" t="s">
         <v>3149</v>
       </c>
@@ -72190,15 +72945,19 @@
         <v>2</v>
       </c>
       <c r="F188" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G188" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="189" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H188" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" ht="17.5" thickBot="1">
       <c r="A189" s="27" t="s">
         <v>3149</v>
       </c>
@@ -72217,15 +72976,19 @@
         <v>2</v>
       </c>
       <c r="F189" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G189" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="190" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H189" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" ht="17.5" thickBot="1">
       <c r="A190" s="27" t="s">
         <v>3149</v>
       </c>
@@ -72244,15 +73007,19 @@
         <v>2</v>
       </c>
       <c r="F190" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G190" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="191" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H190" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" ht="17.5" thickBot="1">
       <c r="A191" s="27" t="s">
         <v>3149</v>
       </c>
@@ -72271,15 +73038,19 @@
         <v>2</v>
       </c>
       <c r="F191" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G191" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="192" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H191" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" ht="17.5" thickBot="1">
       <c r="A192" s="27" t="s">
         <v>3149</v>
       </c>
@@ -72298,15 +73069,19 @@
         <v>5</v>
       </c>
       <c r="F192" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G192" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="193" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H192" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" ht="17.5" thickBot="1">
       <c r="A193" s="27" t="s">
         <v>3149</v>
       </c>
@@ -72325,15 +73100,19 @@
         <v>0</v>
       </c>
       <c r="F193" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G193" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="194" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H193" s="39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" ht="17.5" thickBot="1">
       <c r="A194" s="27" t="s">
         <v>3149</v>
       </c>
@@ -72352,15 +73131,19 @@
         <v>3</v>
       </c>
       <c r="F194" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G194" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="195" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H194" s="39">
+        <f t="shared" ref="H194:H257" si="9">IF(ISNUMBER(SEARCH("M", C194)), 1, 0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" ht="17.5" thickBot="1">
       <c r="A195" s="27" t="s">
         <v>3149</v>
       </c>
@@ -72379,15 +73162,19 @@
         <v>2</v>
       </c>
       <c r="F195" s="34">
-        <f t="shared" ref="F195:F258" si="6">IF(D195&gt;=3,9,0)</f>
+        <f t="shared" ref="F195:F258" si="10">IF(AND(H195=1,D195&gt;=2),9,IF(D195&gt;=3,9,0))</f>
         <v>9</v>
       </c>
       <c r="G195" s="34">
-        <f t="shared" ref="G195:G258" si="7">IF(E195&gt;3,3,E195)</f>
+        <f t="shared" ref="G195:G258" si="11">IF(AND(H195=1,E195&gt;=2),3,IF(E195&gt;3,3,E195))</f>
         <v>2</v>
       </c>
-    </row>
-    <row r="196" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H195" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" ht="17.5" thickBot="1">
       <c r="A196" s="27" t="s">
         <v>3149</v>
       </c>
@@ -72406,15 +73193,19 @@
         <v>3</v>
       </c>
       <c r="F196" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G196" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="197" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H196" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" ht="17.5" thickBot="1">
       <c r="A197" s="27" t="s">
         <v>3149</v>
       </c>
@@ -72433,15 +73224,19 @@
         <v>3</v>
       </c>
       <c r="F197" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G197" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="198" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H197" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" ht="17.5" thickBot="1">
       <c r="A198" s="27" t="s">
         <v>3149</v>
       </c>
@@ -72460,15 +73255,19 @@
         <v>3</v>
       </c>
       <c r="F198" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G198" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="199" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H198" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" ht="17.5" thickBot="1">
       <c r="A199" s="27" t="s">
         <v>3149</v>
       </c>
@@ -72487,15 +73286,19 @@
         <v>4</v>
       </c>
       <c r="F199" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G199" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="200" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H199" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" ht="17.5" thickBot="1">
       <c r="A200" s="27" t="s">
         <v>3149</v>
       </c>
@@ -72514,15 +73317,19 @@
         <v>1</v>
       </c>
       <c r="F200" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G200" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="201" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H200" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" ht="17.5" thickBot="1">
       <c r="A201" s="27" t="s">
         <v>3149</v>
       </c>
@@ -72541,15 +73348,19 @@
         <v>2</v>
       </c>
       <c r="F201" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G201" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="202" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H201" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" ht="17.5" thickBot="1">
       <c r="A202" s="27" t="s">
         <v>3149</v>
       </c>
@@ -72568,15 +73379,19 @@
         <v>3</v>
       </c>
       <c r="F202" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G202" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="203" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H202" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" ht="17.5" thickBot="1">
       <c r="A203" s="27" t="s">
         <v>3149</v>
       </c>
@@ -72595,15 +73410,19 @@
         <v>2</v>
       </c>
       <c r="F203" s="34">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>9</v>
       </c>
       <c r="G203" s="34">
-        <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="204" spans="1:7" ht="17.5" thickBot="1">
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
+      <c r="H203" s="39">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" ht="17.5" thickBot="1">
       <c r="A204" s="27" t="s">
         <v>3149</v>
       </c>
@@ -72622,15 +73441,19 @@
         <v>4</v>
       </c>
       <c r="F204" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G204" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="205" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H204" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" ht="17.5" thickBot="1">
       <c r="A205" s="27" t="s">
         <v>3149</v>
       </c>
@@ -72649,15 +73472,19 @@
         <v>0</v>
       </c>
       <c r="F205" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G205" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="206" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H205" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" ht="17.5" thickBot="1">
       <c r="A206" s="27" t="s">
         <v>3149</v>
       </c>
@@ -72676,15 +73503,19 @@
         <v>2</v>
       </c>
       <c r="F206" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G206" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="207" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H206" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" ht="17.5" thickBot="1">
       <c r="A207" s="27" t="s">
         <v>3149</v>
       </c>
@@ -72703,15 +73534,19 @@
         <v>3</v>
       </c>
       <c r="F207" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G207" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="208" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H207" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" ht="17.5" thickBot="1">
       <c r="A208" s="27" t="s">
         <v>3149</v>
       </c>
@@ -72730,15 +73565,19 @@
         <v>0</v>
       </c>
       <c r="F208" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G208" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="209" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H208" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" ht="17.5" thickBot="1">
       <c r="A209" s="27" t="s">
         <v>3149</v>
       </c>
@@ -72757,15 +73596,19 @@
         <v>0</v>
       </c>
       <c r="F209" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G209" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="210" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H209" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" ht="17.5" thickBot="1">
       <c r="A210" s="27" t="s">
         <v>3149</v>
       </c>
@@ -72784,15 +73627,19 @@
         <v>4</v>
       </c>
       <c r="F210" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G210" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="211" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H210" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" ht="17.5" thickBot="1">
       <c r="A211" s="27" t="s">
         <v>3149</v>
       </c>
@@ -72811,15 +73658,19 @@
         <v>4</v>
       </c>
       <c r="F211" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G211" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="212" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H211" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" ht="17.5" thickBot="1">
       <c r="A212" s="27" t="s">
         <v>3149</v>
       </c>
@@ -72838,15 +73689,19 @@
         <v>4</v>
       </c>
       <c r="F212" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G212" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="213" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H212" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" ht="17.5" thickBot="1">
       <c r="A213" s="27" t="s">
         <v>3149</v>
       </c>
@@ -72865,15 +73720,19 @@
         <v>3</v>
       </c>
       <c r="F213" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G213" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="214" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H213" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" ht="17.5" thickBot="1">
       <c r="A214" s="27" t="s">
         <v>3149</v>
       </c>
@@ -72892,15 +73751,19 @@
         <v>3</v>
       </c>
       <c r="F214" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G214" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="215" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H214" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" ht="17.5" thickBot="1">
       <c r="A215" s="27" t="s">
         <v>3149</v>
       </c>
@@ -72919,15 +73782,19 @@
         <v>3</v>
       </c>
       <c r="F215" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G215" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="216" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H215" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" ht="17.5" thickBot="1">
       <c r="A216" s="27" t="s">
         <v>3149</v>
       </c>
@@ -72946,15 +73813,19 @@
         <v>3</v>
       </c>
       <c r="F216" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G216" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="217" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H216" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" ht="17.5" thickBot="1">
       <c r="A217" s="27" t="s">
         <v>3149</v>
       </c>
@@ -72973,15 +73844,19 @@
         <v>3</v>
       </c>
       <c r="F217" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G217" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="218" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H217" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" ht="17.5" thickBot="1">
       <c r="A218" s="27" t="s">
         <v>3149</v>
       </c>
@@ -73000,15 +73875,19 @@
         <v>3</v>
       </c>
       <c r="F218" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G218" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="219" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H218" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" ht="17.5" thickBot="1">
       <c r="A219" s="27" t="s">
         <v>3149</v>
       </c>
@@ -73027,15 +73906,19 @@
         <v>2</v>
       </c>
       <c r="F219" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G219" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="220" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H219" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" ht="17.5" thickBot="1">
       <c r="A220" s="27" t="s">
         <v>3149</v>
       </c>
@@ -73054,15 +73937,19 @@
         <v>3</v>
       </c>
       <c r="F220" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G220" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="221" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H220" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" ht="17.5" thickBot="1">
       <c r="A221" s="27" t="s">
         <v>3149</v>
       </c>
@@ -73081,15 +73968,19 @@
         <v>2</v>
       </c>
       <c r="F221" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G221" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="222" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H221" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" ht="17.5" thickBot="1">
       <c r="A222" s="27" t="s">
         <v>3149</v>
       </c>
@@ -73108,15 +73999,19 @@
         <v>4</v>
       </c>
       <c r="F222" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G222" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="223" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H222" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" ht="17.5" thickBot="1">
       <c r="A223" s="27" t="s">
         <v>3149</v>
       </c>
@@ -73135,15 +74030,19 @@
         <v>2</v>
       </c>
       <c r="F223" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G223" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="224" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H223" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" ht="17.5" thickBot="1">
       <c r="A224" s="27" t="s">
         <v>3149</v>
       </c>
@@ -73162,15 +74061,19 @@
         <v>3</v>
       </c>
       <c r="F224" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G224" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="225" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H224" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" ht="17.5" thickBot="1">
       <c r="A225" s="27" t="s">
         <v>3149</v>
       </c>
@@ -73189,15 +74092,19 @@
         <v>3</v>
       </c>
       <c r="F225" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G225" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="226" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H225" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" ht="17.5" thickBot="1">
       <c r="A226" s="27" t="s">
         <v>3149</v>
       </c>
@@ -73216,15 +74123,19 @@
         <v>4</v>
       </c>
       <c r="F226" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G226" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="227" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H226" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" ht="17.5" thickBot="1">
       <c r="A227" s="27" t="s">
         <v>3149</v>
       </c>
@@ -73243,15 +74154,19 @@
         <v>3</v>
       </c>
       <c r="F227" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G227" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="228" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H227" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" ht="17.5" thickBot="1">
       <c r="A228" s="27" t="s">
         <v>3149</v>
       </c>
@@ -73270,15 +74185,19 @@
         <v>0</v>
       </c>
       <c r="F228" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G228" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="229" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H228" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" ht="17.5" thickBot="1">
       <c r="A229" s="27" t="s">
         <v>3149</v>
       </c>
@@ -73297,15 +74216,19 @@
         <v>3</v>
       </c>
       <c r="F229" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G229" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="230" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H229" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" ht="17.5" thickBot="1">
       <c r="A230" s="27" t="s">
         <v>3149</v>
       </c>
@@ -73324,15 +74247,19 @@
         <v>3</v>
       </c>
       <c r="F230" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G230" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="231" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H230" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" ht="17.5" thickBot="1">
       <c r="A231" s="27" t="s">
         <v>3149</v>
       </c>
@@ -73351,15 +74278,19 @@
         <v>3</v>
       </c>
       <c r="F231" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G231" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="232" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H231" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" ht="17.5" thickBot="1">
       <c r="A232" s="27" t="s">
         <v>3149</v>
       </c>
@@ -73378,15 +74309,19 @@
         <v>2</v>
       </c>
       <c r="F232" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G232" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="233" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H232" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" ht="17.5" thickBot="1">
       <c r="A233" s="27" t="s">
         <v>3149</v>
       </c>
@@ -73405,15 +74340,19 @@
         <v>3</v>
       </c>
       <c r="F233" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G233" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="234" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H233" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" ht="17.5" thickBot="1">
       <c r="A234" s="27" t="s">
         <v>3149</v>
       </c>
@@ -73432,15 +74371,19 @@
         <v>2</v>
       </c>
       <c r="F234" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G234" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="235" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H234" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" ht="17.5" thickBot="1">
       <c r="A235" s="27" t="s">
         <v>3149</v>
       </c>
@@ -73459,15 +74402,19 @@
         <v>4</v>
       </c>
       <c r="F235" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G235" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="236" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H235" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" ht="17.5" thickBot="1">
       <c r="A236" s="27" t="s">
         <v>3149</v>
       </c>
@@ -73486,15 +74433,19 @@
         <v>3</v>
       </c>
       <c r="F236" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G236" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="237" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H236" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" ht="17.5" thickBot="1">
       <c r="A237" s="27" t="s">
         <v>3149</v>
       </c>
@@ -73513,15 +74464,19 @@
         <v>0</v>
       </c>
       <c r="F237" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G237" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="238" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H237" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" ht="17.5" thickBot="1">
       <c r="A238" s="27" t="s">
         <v>3149</v>
       </c>
@@ -73540,15 +74495,19 @@
         <v>3</v>
       </c>
       <c r="F238" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G238" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="239" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H238" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" ht="17.5" thickBot="1">
       <c r="A239" s="27" t="s">
         <v>3149</v>
       </c>
@@ -73567,15 +74526,19 @@
         <v>0</v>
       </c>
       <c r="F239" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G239" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="240" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H239" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" ht="17.5" thickBot="1">
       <c r="A240" s="27" t="s">
         <v>3149</v>
       </c>
@@ -73594,15 +74557,19 @@
         <v>0</v>
       </c>
       <c r="F240" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G240" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="241" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H240" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" ht="17.5" thickBot="1">
       <c r="A241" s="27" t="s">
         <v>3149</v>
       </c>
@@ -73621,15 +74588,19 @@
         <v>5</v>
       </c>
       <c r="F241" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G241" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="242" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H241" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" ht="17.5" thickBot="1">
       <c r="A242" s="27" t="s">
         <v>3149</v>
       </c>
@@ -73648,15 +74619,19 @@
         <v>3</v>
       </c>
       <c r="F242" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G242" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="243" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H242" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" ht="17.5" thickBot="1">
       <c r="A243" s="27" t="s">
         <v>3149</v>
       </c>
@@ -73675,15 +74650,19 @@
         <v>0</v>
       </c>
       <c r="F243" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G243" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="244" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H243" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" ht="17.5" thickBot="1">
       <c r="A244" s="27" t="s">
         <v>3149</v>
       </c>
@@ -73702,15 +74681,19 @@
         <v>3</v>
       </c>
       <c r="F244" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G244" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="245" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H244" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" ht="17.5" thickBot="1">
       <c r="A245" s="27" t="s">
         <v>3149</v>
       </c>
@@ -73729,15 +74712,19 @@
         <v>2</v>
       </c>
       <c r="F245" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G245" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="246" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H245" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" ht="17.5" thickBot="1">
       <c r="A246" s="27" t="s">
         <v>3149</v>
       </c>
@@ -73756,15 +74743,19 @@
         <v>2</v>
       </c>
       <c r="F246" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G246" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="247" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H246" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" ht="17.5" thickBot="1">
       <c r="A247" s="27" t="s">
         <v>3149</v>
       </c>
@@ -73783,15 +74774,19 @@
         <v>3</v>
       </c>
       <c r="F247" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G247" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="248" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H247" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" ht="17.5" thickBot="1">
       <c r="A248" s="27" t="s">
         <v>3149</v>
       </c>
@@ -73810,15 +74805,19 @@
         <v>2</v>
       </c>
       <c r="F248" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G248" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="249" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H248" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" ht="17.5" thickBot="1">
       <c r="A249" s="27" t="s">
         <v>3149</v>
       </c>
@@ -73837,15 +74836,19 @@
         <v>3</v>
       </c>
       <c r="F249" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G249" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="250" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H249" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" ht="17.5" thickBot="1">
       <c r="A250" s="27" t="s">
         <v>3149</v>
       </c>
@@ -73864,15 +74867,19 @@
         <v>0</v>
       </c>
       <c r="F250" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G250" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="251" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H250" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" ht="17.5" thickBot="1">
       <c r="A251" s="27" t="s">
         <v>3149</v>
       </c>
@@ -73891,15 +74898,19 @@
         <v>2</v>
       </c>
       <c r="F251" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G251" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="252" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H251" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" ht="17.5" thickBot="1">
       <c r="A252" s="27" t="s">
         <v>3149</v>
       </c>
@@ -73918,15 +74929,19 @@
         <v>3</v>
       </c>
       <c r="F252" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G252" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="253" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H252" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" ht="17.5" thickBot="1">
       <c r="A253" s="27" t="s">
         <v>3149</v>
       </c>
@@ -73945,15 +74960,19 @@
         <v>3</v>
       </c>
       <c r="F253" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G253" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="254" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H253" s="39">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" ht="17.5" thickBot="1">
       <c r="A254" s="27" t="s">
         <v>3149</v>
       </c>
@@ -73972,15 +74991,19 @@
         <v>2</v>
       </c>
       <c r="F254" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G254" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="255" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H254" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" ht="17.5" thickBot="1">
       <c r="A255" s="27" t="s">
         <v>3149</v>
       </c>
@@ -73999,15 +75022,19 @@
         <v>3</v>
       </c>
       <c r="F255" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G255" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="256" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H255" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" ht="17.5" thickBot="1">
       <c r="A256" s="27" t="s">
         <v>3149</v>
       </c>
@@ -74026,15 +75053,19 @@
         <v>2</v>
       </c>
       <c r="F256" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G256" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="257" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H256" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" ht="17.5" thickBot="1">
       <c r="A257" s="27" t="s">
         <v>3149</v>
       </c>
@@ -74053,15 +75084,19 @@
         <v>3</v>
       </c>
       <c r="F257" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G257" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="258" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H257" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" ht="17.5" thickBot="1">
       <c r="A258" s="27" t="s">
         <v>3149</v>
       </c>
@@ -74080,15 +75115,19 @@
         <v>3</v>
       </c>
       <c r="F258" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="G258" s="34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="259" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H258" s="39">
+        <f t="shared" ref="H258:H288" si="12">IF(ISNUMBER(SEARCH("M", C258)), 1, 0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" ht="17.5" thickBot="1">
       <c r="A259" s="27" t="s">
         <v>3149</v>
       </c>
@@ -74107,15 +75146,19 @@
         <v>3</v>
       </c>
       <c r="F259" s="34">
-        <f t="shared" ref="F259:F288" si="8">IF(D259&gt;=3,9,0)</f>
+        <f t="shared" ref="F259:F288" si="13">IF(AND(H259=1,D259&gt;=2),9,IF(D259&gt;=3,9,0))</f>
         <v>9</v>
       </c>
       <c r="G259" s="34">
-        <f t="shared" ref="G259:G288" si="9">IF(E259&gt;3,3,E259)</f>
+        <f t="shared" ref="G259:G288" si="14">IF(AND(H259=1,E259&gt;=2),3,IF(E259&gt;3,3,E259))</f>
         <v>3</v>
       </c>
-    </row>
-    <row r="260" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H259" s="39">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" ht="17.5" thickBot="1">
       <c r="A260" s="27" t="s">
         <v>3149</v>
       </c>
@@ -74134,15 +75177,19 @@
         <v>5</v>
       </c>
       <c r="F260" s="34">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>9</v>
       </c>
       <c r="G260" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="261" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H260" s="39">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" ht="17.5" thickBot="1">
       <c r="A261" s="27" t="s">
         <v>3149</v>
       </c>
@@ -74161,15 +75208,19 @@
         <v>3</v>
       </c>
       <c r="F261" s="34">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>9</v>
       </c>
       <c r="G261" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="262" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H261" s="39">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" ht="17.5" thickBot="1">
       <c r="A262" s="27" t="s">
         <v>3149</v>
       </c>
@@ -74188,15 +75239,19 @@
         <v>2</v>
       </c>
       <c r="F262" s="34">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="G262" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="263" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H262" s="39">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" ht="17.5" thickBot="1">
       <c r="A263" s="27" t="s">
         <v>3149</v>
       </c>
@@ -74215,15 +75270,19 @@
         <v>2</v>
       </c>
       <c r="F263" s="34">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="G263" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="264" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H263" s="39">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" ht="17.5" thickBot="1">
       <c r="A264" s="27" t="s">
         <v>3149</v>
       </c>
@@ -74242,15 +75301,19 @@
         <v>3</v>
       </c>
       <c r="F264" s="34">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>9</v>
       </c>
       <c r="G264" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="265" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H264" s="39">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" ht="17.5" thickBot="1">
       <c r="A265" s="27" t="s">
         <v>3149</v>
       </c>
@@ -74269,15 +75332,19 @@
         <v>3</v>
       </c>
       <c r="F265" s="34">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>9</v>
       </c>
       <c r="G265" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="266" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H265" s="39">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" ht="17.5" thickBot="1">
       <c r="A266" s="27" t="s">
         <v>3149</v>
       </c>
@@ -74296,15 +75363,19 @@
         <v>2</v>
       </c>
       <c r="F266" s="34">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="G266" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="267" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H266" s="39">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" ht="17.5" thickBot="1">
       <c r="A267" s="27" t="s">
         <v>3149</v>
       </c>
@@ -74323,15 +75394,19 @@
         <v>3</v>
       </c>
       <c r="F267" s="34">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>9</v>
       </c>
       <c r="G267" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="268" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H267" s="39">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" ht="17.5" thickBot="1">
       <c r="A268" s="27" t="s">
         <v>3149</v>
       </c>
@@ -74350,15 +75425,19 @@
         <v>3</v>
       </c>
       <c r="F268" s="34">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>9</v>
       </c>
       <c r="G268" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="269" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H268" s="39">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" ht="17.5" thickBot="1">
       <c r="A269" s="27" t="s">
         <v>3149</v>
       </c>
@@ -74377,15 +75456,19 @@
         <v>3</v>
       </c>
       <c r="F269" s="34">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>9</v>
       </c>
       <c r="G269" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="270" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H269" s="39">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" ht="17.5" thickBot="1">
       <c r="A270" s="27" t="s">
         <v>3149</v>
       </c>
@@ -74404,15 +75487,19 @@
         <v>2</v>
       </c>
       <c r="F270" s="34">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>9</v>
       </c>
       <c r="G270" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="271" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H270" s="39">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" ht="17.5" thickBot="1">
       <c r="A271" s="27" t="s">
         <v>3149</v>
       </c>
@@ -74431,15 +75518,19 @@
         <v>4</v>
       </c>
       <c r="F271" s="34">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>9</v>
       </c>
       <c r="G271" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="272" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H271" s="39">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8" ht="17.5" thickBot="1">
       <c r="A272" s="27" t="s">
         <v>3149</v>
       </c>
@@ -74458,15 +75549,19 @@
         <v>3</v>
       </c>
       <c r="F272" s="34">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>9</v>
       </c>
       <c r="G272" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="273" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H272" s="39">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" ht="17.5" thickBot="1">
       <c r="A273" s="27" t="s">
         <v>3149</v>
       </c>
@@ -74485,15 +75580,19 @@
         <v>3</v>
       </c>
       <c r="F273" s="34">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>9</v>
       </c>
       <c r="G273" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="274" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H273" s="39">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" ht="17.5" thickBot="1">
       <c r="A274" s="27" t="s">
         <v>3149</v>
       </c>
@@ -74512,15 +75611,19 @@
         <v>3</v>
       </c>
       <c r="F274" s="34">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>9</v>
       </c>
       <c r="G274" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="275" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H274" s="39">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" ht="17.5" thickBot="1">
       <c r="A275" s="27" t="s">
         <v>3149</v>
       </c>
@@ -74539,15 +75642,19 @@
         <v>3</v>
       </c>
       <c r="F275" s="34">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>9</v>
       </c>
       <c r="G275" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="276" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H275" s="39">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" ht="17.5" thickBot="1">
       <c r="A276" s="27" t="s">
         <v>3149</v>
       </c>
@@ -74566,15 +75673,19 @@
         <v>3</v>
       </c>
       <c r="F276" s="34">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>9</v>
       </c>
       <c r="G276" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="277" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H276" s="39">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" ht="17.5" thickBot="1">
       <c r="A277" s="27" t="s">
         <v>3149</v>
       </c>
@@ -74593,15 +75704,19 @@
         <v>1</v>
       </c>
       <c r="F277" s="34">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="G277" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="278" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H277" s="39">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" ht="17.5" thickBot="1">
       <c r="A278" s="27" t="s">
         <v>3149</v>
       </c>
@@ -74620,15 +75735,19 @@
         <v>3</v>
       </c>
       <c r="F278" s="34">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>9</v>
       </c>
       <c r="G278" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="279" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H278" s="39">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" ht="17.5" thickBot="1">
       <c r="A279" s="27" t="s">
         <v>3149</v>
       </c>
@@ -74647,15 +75766,19 @@
         <v>7</v>
       </c>
       <c r="F279" s="34">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>9</v>
       </c>
       <c r="G279" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="280" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H279" s="39">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8" ht="17.5" thickBot="1">
       <c r="A280" s="27" t="s">
         <v>3149</v>
       </c>
@@ -74674,15 +75797,19 @@
         <v>5</v>
       </c>
       <c r="F280" s="34">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>9</v>
       </c>
       <c r="G280" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="281" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H280" s="39">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" ht="17.5" thickBot="1">
       <c r="A281" s="27" t="s">
         <v>3149</v>
       </c>
@@ -74701,15 +75828,19 @@
         <v>6</v>
       </c>
       <c r="F281" s="34">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>9</v>
       </c>
       <c r="G281" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="282" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H281" s="39">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" ht="17.5" thickBot="1">
       <c r="A282" s="27" t="s">
         <v>3149</v>
       </c>
@@ -74728,15 +75859,19 @@
         <v>5</v>
       </c>
       <c r="F282" s="34">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>9</v>
       </c>
       <c r="G282" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="283" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H282" s="39">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" ht="17.5" thickBot="1">
       <c r="A283" s="27" t="s">
         <v>3149</v>
       </c>
@@ -74755,15 +75890,19 @@
         <v>8</v>
       </c>
       <c r="F283" s="34">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>9</v>
       </c>
       <c r="G283" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="284" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H283" s="39">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" ht="17.5" thickBot="1">
       <c r="A284" s="27" t="s">
         <v>3149</v>
       </c>
@@ -74782,15 +75921,19 @@
         <v>5</v>
       </c>
       <c r="F284" s="34">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>9</v>
       </c>
       <c r="G284" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="285" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H284" s="39">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8" ht="17.5" thickBot="1">
       <c r="A285" s="27" t="s">
         <v>3149</v>
       </c>
@@ -74809,15 +75952,19 @@
         <v>3</v>
       </c>
       <c r="F285" s="34">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>9</v>
       </c>
       <c r="G285" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="286" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H285" s="39">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" ht="17.5" thickBot="1">
       <c r="A286" s="27" t="s">
         <v>3149</v>
       </c>
@@ -74836,15 +75983,19 @@
         <v>4</v>
       </c>
       <c r="F286" s="34">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>9</v>
       </c>
       <c r="G286" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="287" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H286" s="39">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" ht="17.5" thickBot="1">
       <c r="A287" s="27" t="s">
         <v>3149</v>
       </c>
@@ -74863,15 +76014,19 @@
         <v>6</v>
       </c>
       <c r="F287" s="34">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>9</v>
       </c>
       <c r="G287" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="288" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H287" s="39">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" ht="17.5" thickBot="1">
       <c r="A288" s="27" t="s">
         <v>3149</v>
       </c>
@@ -74890,15 +76045,20 @@
         <v>3</v>
       </c>
       <c r="F288" s="34">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>9</v>
       </c>
       <c r="G288" s="34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
+      <c r="H288" s="39">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H288" xr:uid="{BD3DA3E8-EF64-4E97-8A3D-A087070FCC04}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
